--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/WASHINGTON_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/WASHINGTON_2015.xlsx
@@ -427,7 +427,7 @@
         <v>14</v>
       </c>
       <c r="D4">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="5">
@@ -3019,7 +3019,7 @@
         <v>14</v>
       </c>
       <c r="D148">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="149">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C274">
@@ -5521,7 +5521,7 @@
         <v>14</v>
       </c>
       <c r="D287">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="288">
@@ -5953,7 +5953,7 @@
         <v>14</v>
       </c>
       <c r="D311">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="312">
@@ -6133,7 +6133,7 @@
         <v>14</v>
       </c>
       <c r="D321">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="322">
@@ -6331,7 +6331,7 @@
         <v>14</v>
       </c>
       <c r="D332">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="333">
@@ -6349,7 +6349,7 @@
         <v>14</v>
       </c>
       <c r="D333">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="334">
@@ -7501,7 +7501,7 @@
         <v>14</v>
       </c>
       <c r="D397">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="398">
@@ -7753,7 +7753,7 @@
         <v>14</v>
       </c>
       <c r="D411">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="412">
@@ -9031,7 +9031,7 @@
         <v>14</v>
       </c>
       <c r="D482">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="483">
@@ -9913,7 +9913,7 @@
         <v>14</v>
       </c>
       <c r="D531">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="532">
@@ -10633,7 +10633,7 @@
         <v>14</v>
       </c>
       <c r="D571">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="572">
@@ -11569,7 +11569,7 @@
         <v>14</v>
       </c>
       <c r="D623">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="624">
@@ -11965,7 +11965,7 @@
         <v>14</v>
       </c>
       <c r="D645">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="646">
@@ -13333,7 +13333,7 @@
         <v>130</v>
       </c>
       <c r="D721">
-        <v>0.009283724916089409</v>
+        <v>0.009283724916089408</v>
       </c>
     </row>
     <row r="722">
@@ -13603,7 +13603,7 @@
         <v>14</v>
       </c>
       <c r="D736">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="737">
@@ -14251,7 +14251,7 @@
         <v>14</v>
       </c>
       <c r="D772">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="773">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C808">
@@ -14910,7 +14910,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C809">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C864">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C865">
@@ -17581,7 +17581,7 @@
         <v>14</v>
       </c>
       <c r="D957">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="958">
@@ -21469,7 +21469,7 @@
         <v>14</v>
       </c>
       <c r="D1173">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="1174">
@@ -25231,7 +25231,7 @@
         <v>14</v>
       </c>
       <c r="D1382">
-        <v>0.0009997857601942441</v>
+        <v>0.0009997857601942439</v>
       </c>
     </row>
     <row r="1383">
